--- a/Додаток_4_3.xlsx
+++ b/Додаток_4_3.xlsx
@@ -1811,7 +1811,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="L403" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -19379,7 +19379,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="L433" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -20035,7 +20035,7 @@
       </c>
       <c r="L447" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="L467" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -21515,7 +21515,7 @@
       </c>
       <c r="L481" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21601,7 @@
       </c>
       <c r="L483" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -21899,7 +21899,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="L491" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -22337,7 +22337,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="L501" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -22425,7 +22425,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="L515" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="L519" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -24865,7 +24865,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -24907,7 +24907,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -25111,7 +25111,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -25153,7 +25153,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -25275,7 +25275,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -25565,7 +25565,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -26443,7 +26443,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -26525,7 +26525,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -28617,7 +28617,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -29413,7 +29413,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -30161,7 +30161,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -30285,7 +30285,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -30867,7 +30867,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -37159,7 +37159,7 @@
       </c>
       <c r="L333" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -38371,7 +38371,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -38411,7 +38411,7 @@
       </c>
       <c r="L363" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -39285,7 +39285,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -39325,7 +39325,7 @@
       </c>
       <c r="L385" s="4" t="inlineStr">
         <is>
-          <t>дим</t>
+          <t>туман</t>
         </is>
       </c>
     </row>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>ожеледь</t>
+          <t>гроза</t>
         </is>
       </c>
     </row>
@@ -39911,7 +39911,7 @@
       </c>
       <c r="L399" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -39953,7 +39953,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -39995,7 +39995,7 @@
       </c>
       <c r="L401" s="4" t="inlineStr">
         <is>
-          <t>сніг</t>
+          <t>дощ</t>
         </is>
       </c>
     </row>
@@ -40539,7 +40539,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
@@ -40705,7 +40705,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>злива</t>
+          <t>сніг</t>
         </is>
       </c>
     </row>
